--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][CI]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][CI]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>9.123267865290138</v>
+        <v>9.189725599341129</v>
       </c>
       <c r="D2" t="n">
-        <v>5.170876119161903</v>
+        <v>4.956995582556379</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>9.977797419182965</v>
+        <v>9.760341584390744</v>
       </c>
       <c r="G2" t="n">
-        <v>2.491685529360061</v>
+        <v>2.402093033993324</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>392</v>
+        <v>447</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8476785709354919</v>
+        <v>0.9945964156639604</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,28 +540,28 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>9.169293767306378</v>
+        <v>9.128953221820622</v>
       </c>
       <c r="D3" t="n">
-        <v>5.59233499524674</v>
+        <v>5.675584772206828</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5387800932175</v>
+        <v>10.67660196726984</v>
       </c>
       <c r="G3" t="n">
-        <v>1.812271360163325</v>
+        <v>2.07209040732464</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1787645672028489</v>
+        <v>0.1416648172079989</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -568,28 +580,28 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>11.48113308787037</v>
+        <v>11.2463652262944</v>
       </c>
       <c r="D4" t="n">
-        <v>4.164919934646322</v>
+        <v>4.002489388674579</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>11.0483852375959</v>
+        <v>10.57390732249515</v>
       </c>
       <c r="G4" t="n">
-        <v>2.561594578022276</v>
+        <v>2.900868824894132</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9602826914358614</v>
+        <v>0.7708869388294171</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>10.65384749907279</v>
+        <v>10.48903685425709</v>
       </c>
       <c r="D5" t="n">
-        <v>3.578250841302442</v>
+        <v>3.350613637474255</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>15.90655366516374</v>
+        <v>15.60358439267195</v>
       </c>
       <c r="G5" t="n">
-        <v>1.854806483731019</v>
+        <v>2.187552913089103</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="J5" t="n">
-        <v>1.942210181996216e-06</v>
+        <v>1.926116027853009e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>5.826630545988646e-05</v>
+        <v>5.778348083559027e-05</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,28 +660,28 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>12.61830695445549</v>
+        <v>12.83852046116042</v>
       </c>
       <c r="D6" t="n">
-        <v>4.958321154467565</v>
+        <v>4.959725889551693</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>12.62834777314463</v>
+        <v>12.62034250805338</v>
       </c>
       <c r="G6" t="n">
-        <v>2.893255116501725</v>
+        <v>2.709928614550305</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>438</v>
+        <v>499</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6540163995069548</v>
+        <v>0.4939647584310011</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -688,28 +700,28 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>10.26778072270396</v>
+        <v>10.17162787796864</v>
       </c>
       <c r="D7" t="n">
-        <v>4.947068703869856</v>
+        <v>4.971418294509519</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>12.30119414494654</v>
+        <v>12.45215535796531</v>
       </c>
       <c r="G7" t="n">
-        <v>2.294876601491395</v>
+        <v>2.567823750864173</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1978658378562647</v>
+        <v>0.1309785704860878</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -728,28 +740,28 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>10.86599611237921</v>
+        <v>10.88131861258884</v>
       </c>
       <c r="D8" t="n">
-        <v>4.51950235494277</v>
+        <v>4.583550177487568</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>9.64734964959675</v>
+        <v>10.05601328419887</v>
       </c>
       <c r="G8" t="n">
-        <v>1.786155681182531</v>
+        <v>1.990146865155123</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2640298878473034</v>
+        <v>0.397243176674534</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -768,28 +780,28 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>10.81993113588531</v>
+        <v>10.74450785908631</v>
       </c>
       <c r="D9" t="n">
-        <v>5.656378163336647</v>
+        <v>5.677707690918119</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>13.7668221681493</v>
+        <v>13.74311585215333</v>
       </c>
       <c r="G9" t="n">
-        <v>3.893213630793177</v>
+        <v>3.678711300457649</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1834061326016969</v>
+        <v>0.1491529689594686</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -808,28 +820,28 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>10.11488677865225</v>
+        <v>10.0037256153434</v>
       </c>
       <c r="D10" t="n">
-        <v>3.206079395265528</v>
+        <v>3.147860144092193</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
-        <v>11.25408937983144</v>
+        <v>11.2521356859956</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02491179414202</v>
+        <v>1.894344254486227</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2028663952103028</v>
+        <v>0.145371973842238</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -848,28 +860,28 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>10.38942405867255</v>
+        <v>10.30063208567216</v>
       </c>
       <c r="D11" t="n">
-        <v>4.316283508006743</v>
+        <v>4.099139011022001</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>11.65881101426638</v>
+        <v>11.43594072018104</v>
       </c>
       <c r="G11" t="n">
-        <v>2.180570866134254</v>
+        <v>2.163011949886279</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1226455091309025</v>
+        <v>0.145371973842238</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>10.53299789848648</v>
+        <v>10.62045425482738</v>
       </c>
       <c r="D12" t="n">
-        <v>3.770546692406563</v>
+        <v>3.83254148980158</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>15.7491528820766</v>
+        <v>15.76095535576302</v>
       </c>
       <c r="G12" t="n">
-        <v>1.210348144919714</v>
+        <v>1.601674897613237</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="J12" t="n">
-        <v>3.381779362614528e-07</v>
+        <v>2.948062705998656e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>1.014533808784358e-05</v>
+        <v>8.844188117995967e-06</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22542345784808</v>
+        <v>12.39079442279439</v>
       </c>
       <c r="D13" t="n">
-        <v>4.169529555083614</v>
+        <v>4.309150628974098</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>12.031331700178</v>
+        <v>12.36833609299911</v>
       </c>
       <c r="G13" t="n">
-        <v>1.979020250773006</v>
+        <v>2.232820833012497</v>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9602826914358614</v>
+        <v>0.9298435128558283</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,28 +980,28 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>10.29291580111528</v>
+        <v>10.02517442208863</v>
       </c>
       <c r="D14" t="n">
-        <v>4.159514573655869</v>
+        <v>3.81274704755775</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>9.643789451879744</v>
+        <v>9.307529009870592</v>
       </c>
       <c r="G14" t="n">
-        <v>0.866328930782691</v>
+        <v>1.205208931619681</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2579940372154104</v>
+        <v>0.1958257004291746</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1008,28 +1020,28 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>12.52407651459458</v>
+        <v>12.67354452769858</v>
       </c>
       <c r="D15" t="n">
-        <v>2.938288964157801</v>
+        <v>2.768596725205256</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F15" t="n">
-        <v>13.33536400265943</v>
+        <v>13.25845009997353</v>
       </c>
       <c r="G15" t="n">
-        <v>2.406657355789449</v>
+        <v>2.347524011434953</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>338</v>
+        <v>392</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3368508232173144</v>
+        <v>0.4522068978286441</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1048,28 +1060,28 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>9.284471772896461</v>
+        <v>9.258558283082063</v>
       </c>
       <c r="D16" t="n">
-        <v>3.238972836251253</v>
+        <v>3.194673012806482</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>10.84455007329819</v>
+        <v>10.89897001710257</v>
       </c>
       <c r="G16" t="n">
-        <v>2.781989691922948</v>
+        <v>2.606495475817514</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1003081183556453</v>
+        <v>0.05528868712423748</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1088,31 +1100,31 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>12.19860079200818</v>
+        <v>11.89283427735023</v>
       </c>
       <c r="D17" t="n">
-        <v>3.897457547007655</v>
+        <v>3.6841752437925</v>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" t="n">
-        <v>13.93170931935</v>
+        <v>14.24129006256955</v>
       </c>
       <c r="G17" t="n">
-        <v>1.666813138385813</v>
+        <v>1.764854625376287</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1370541505878149</v>
+        <v>0.02018199653963573</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.605459896189072</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1128,28 +1140,28 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>11.07365303034727</v>
+        <v>11.13117232406051</v>
       </c>
       <c r="D18" t="n">
-        <v>5.825918805710947</v>
+        <v>5.814363037910889</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>11.75278427836149</v>
+        <v>12.04070006827311</v>
       </c>
       <c r="G18" t="n">
-        <v>2.201971168824873</v>
+        <v>2.223407545371905</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3090016290700639</v>
+        <v>0.2254102553836667</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1168,28 +1180,28 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>9.978368592964181</v>
+        <v>10.1349010673089</v>
       </c>
       <c r="D19" t="n">
-        <v>5.382186597773963</v>
+        <v>5.233796666084133</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>9.766897626716636</v>
+        <v>9.467606137608335</v>
       </c>
       <c r="G19" t="n">
-        <v>2.820500202433201</v>
+        <v>2.810819093919414</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>456</v>
+        <v>530</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4812472901827335</v>
+        <v>0.269633140627457</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1208,31 +1220,31 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>11.12349168528267</v>
+        <v>11.27253866287737</v>
       </c>
       <c r="D20" t="n">
-        <v>3.757931213046855</v>
+        <v>3.792321725033952</v>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>13.38844359572972</v>
+        <v>13.49960678053517</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64338692900626</v>
+        <v>2.640600337134539</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02502945776115344</v>
+        <v>0.0232824660454801</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7508837328346033</v>
+        <v>0.6984739813644029</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1248,28 +1260,28 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>10.00375270106086</v>
+        <v>10.0676756619945</v>
       </c>
       <c r="D21" t="n">
-        <v>4.124054095758703</v>
+        <v>4.051680423336055</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F21" t="n">
-        <v>10.63839940566639</v>
+        <v>11.25089171774891</v>
       </c>
       <c r="G21" t="n">
-        <v>1.941564848160339</v>
+        <v>2.636662811242774</v>
       </c>
       <c r="H21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7596753363103432</v>
+        <v>0.4202887426699178</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1288,31 +1300,31 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>10.33344856071387</v>
+        <v>10.18393162772598</v>
       </c>
       <c r="D22" t="n">
-        <v>4.433002912344991</v>
+        <v>4.115842715861645</v>
       </c>
       <c r="E22" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F22" t="n">
-        <v>13.60224483508997</v>
+        <v>13.53251009646681</v>
       </c>
       <c r="G22" t="n">
-        <v>1.845948120892396</v>
+        <v>2.011298917916104</v>
       </c>
       <c r="H22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="J22" t="n">
-        <v>0.01022289528989159</v>
+        <v>0.003512443053041098</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3066868586967477</v>
+        <v>0.1053732915912329</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1328,31 +1340,31 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>10.2021486873853</v>
+        <v>9.792292161128568</v>
       </c>
       <c r="D23" t="n">
-        <v>4.873012720267145</v>
+        <v>4.453468860465827</v>
       </c>
       <c r="E23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F23" t="n">
-        <v>12.32400605469563</v>
+        <v>12.11096580614512</v>
       </c>
       <c r="G23" t="n">
-        <v>1.562077543805184</v>
+        <v>1.585161187673431</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="J23" t="n">
-        <v>0.04408350501108833</v>
+        <v>0.01946561709940857</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.5839685129822569</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1368,28 +1380,28 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>13.76644074462543</v>
+        <v>13.76360151175159</v>
       </c>
       <c r="D24" t="n">
-        <v>3.814293724417328</v>
+        <v>3.232012421088677</v>
       </c>
       <c r="E24" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F24" t="n">
-        <v>11.80985897636476</v>
+        <v>12.05408077493532</v>
       </c>
       <c r="G24" t="n">
-        <v>5.077280919070586</v>
+        <v>4.970172340949687</v>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05386426867188614</v>
+        <v>0.06645660848381499</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1408,31 +1420,31 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.84052112719888</v>
+        <v>9.935861500566919</v>
       </c>
       <c r="D25" t="n">
-        <v>3.85055177515691</v>
+        <v>3.918600109223999</v>
       </c>
       <c r="E25" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F25" t="n">
-        <v>13.17602608164337</v>
+        <v>12.77327435808761</v>
       </c>
       <c r="G25" t="n">
-        <v>2.328187644424178</v>
+        <v>2.474816384500424</v>
       </c>
       <c r="H25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001970504691539685</v>
+        <v>0.006347018919467256</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05911514074619056</v>
+        <v>0.1904105675840177</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1448,31 +1460,31 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>10.21702073271644</v>
+        <v>10.34707595506331</v>
       </c>
       <c r="D26" t="n">
-        <v>3.545147171949095</v>
+        <v>3.398815999047183</v>
       </c>
       <c r="E26" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F26" t="n">
-        <v>12.84148445259164</v>
+        <v>13.07501408823992</v>
       </c>
       <c r="G26" t="n">
-        <v>3.078693666322023</v>
+        <v>2.965359574045735</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02693273665086253</v>
+        <v>0.008768912357824662</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8079820995258759</v>
+        <v>0.2630673707347398</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>8.141004111020157</v>
+        <v>8.02217360995081</v>
       </c>
       <c r="D27" t="n">
-        <v>4.348162669103808</v>
+        <v>4.379103907844063</v>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F27" t="n">
-        <v>13.30070735809308</v>
+        <v>13.51712433393002</v>
       </c>
       <c r="G27" t="n">
-        <v>2.524945905957514</v>
+        <v>2.462220060719838</v>
       </c>
       <c r="H27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J27" t="n">
-        <v>7.414887107441783e-05</v>
+        <v>1.177196133631331e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>0.002224466132232535</v>
+        <v>0.0003531588400893993</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,28 +1540,28 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>10.52904745009941</v>
+        <v>10.74579883255413</v>
       </c>
       <c r="D28" t="n">
-        <v>5.046256589678593</v>
+        <v>4.976403691020439</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F28" t="n">
-        <v>9.815111525876699</v>
+        <v>9.927181412836505</v>
       </c>
       <c r="G28" t="n">
-        <v>1.448745869572891</v>
+        <v>1.397212114285852</v>
       </c>
       <c r="H28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>467</v>
+        <v>518</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3893435159406129</v>
+        <v>0.3465156829016796</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>9.575069317591192</v>
+        <v>9.432220452228053</v>
       </c>
       <c r="D29" t="n">
-        <v>4.083043294546611</v>
+        <v>4.037955747994912</v>
       </c>
       <c r="E29" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F29" t="n">
-        <v>16.06340955559478</v>
+        <v>16.40746337613193</v>
       </c>
       <c r="G29" t="n">
-        <v>2.458235089534104</v>
+        <v>2.490385569280351</v>
       </c>
       <c r="H29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J29" t="n">
-        <v>2.397460515407622e-06</v>
+        <v>2.374084039139869e-07</v>
       </c>
       <c r="K29" t="n">
-        <v>7.192381546222866e-05</v>
+        <v>7.122252117419609e-06</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,28 +1620,28 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>12.72390376725254</v>
+        <v>12.71824499231734</v>
       </c>
       <c r="D30" t="n">
-        <v>4.771026935133182</v>
+        <v>4.866323029641971</v>
       </c>
       <c r="E30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F30" t="n">
-        <v>13.39107743720405</v>
+        <v>13.31609757426566</v>
       </c>
       <c r="G30" t="n">
-        <v>2.872730531222124</v>
+        <v>2.965768857472492</v>
       </c>
       <c r="H30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8143903909988228</v>
+        <v>0.886905248410112</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1648,28 +1660,28 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.80818980799316</v>
+        <v>10.73912882097021</v>
       </c>
       <c r="D31" t="n">
-        <v>3.46704073131516</v>
+        <v>3.329769727440866</v>
       </c>
       <c r="E31" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F31" t="n">
-        <v>11.83951836840664</v>
+        <v>11.62705819766195</v>
       </c>
       <c r="G31" t="n">
-        <v>4.822167754802005</v>
+        <v>4.704733411126798</v>
       </c>
       <c r="H31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8254524006382234</v>
+        <v>0.919084811177645</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>74.5438517415903</v>
+        <v>75.06426940556025</v>
       </c>
       <c r="D32" t="n">
-        <v>15.29913842137615</v>
+        <v>15.32753118926624</v>
       </c>
       <c r="E32" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F32" t="n">
-        <v>85.60201586800362</v>
+        <v>85.47048252767574</v>
       </c>
       <c r="G32" t="n">
-        <v>6.661200986455211</v>
+        <v>6.449967096520274</v>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01303440591605395</v>
+        <v>0.0168175942415929</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3910321774816186</v>
+        <v>0.5045278272477871</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1728,28 +1740,28 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>71.56447638403746</v>
+        <v>71.74262691330281</v>
       </c>
       <c r="D33" t="n">
-        <v>9.979747148893031</v>
+        <v>10.35895587535455</v>
       </c>
       <c r="E33" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F33" t="n">
-        <v>76.11714298446766</v>
+        <v>75.84570027354178</v>
       </c>
       <c r="G33" t="n">
-        <v>5.216951975778596</v>
+        <v>5.382271390037921</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="J33" t="n">
-        <v>0.06966224169604796</v>
+        <v>0.1114918118227829</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>69.9094378083842</v>
+        <v>69.85804614661393</v>
       </c>
       <c r="D34" t="n">
-        <v>9.045502904615624</v>
+        <v>9.109967437969759</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F34" t="n">
-        <v>84.0469235964807</v>
+        <v>84.96081033671516</v>
       </c>
       <c r="G34" t="n">
-        <v>3.643450757412811</v>
+        <v>4.265428664441745</v>
       </c>
       <c r="H34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J34" t="n">
-        <v>2.235378972929765e-06</v>
+        <v>5.591034650638886e-07</v>
       </c>
       <c r="K34" t="n">
-        <v>6.706136918789293e-05</v>
+        <v>1.677310395191666e-05</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,31 +1820,31 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>71.35366396829956</v>
+        <v>71.41609640684158</v>
       </c>
       <c r="D35" t="n">
-        <v>11.31214791793061</v>
+        <v>11.57553450268423</v>
       </c>
       <c r="E35" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F35" t="n">
-        <v>78.11425163646565</v>
+        <v>77.82472091949214</v>
       </c>
       <c r="G35" t="n">
-        <v>6.510450023973584</v>
+        <v>6.752328540453849</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0259660236580474</v>
+        <v>0.03518446804048733</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7789807097414221</v>
+        <v>1</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1848,34 +1860,34 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>67.83349279207042</v>
+        <v>67.83897429293786</v>
       </c>
       <c r="D36" t="n">
-        <v>11.45688250825062</v>
+        <v>11.54179679075972</v>
       </c>
       <c r="E36" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F36" t="n">
-        <v>77.80368605882923</v>
+        <v>78.9538926859386</v>
       </c>
       <c r="G36" t="n">
-        <v>6.819871906042926</v>
+        <v>7.086257249788876</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J36" t="n">
-        <v>0.003618047076354066</v>
+        <v>0.0006579250515224295</v>
       </c>
       <c r="K36" t="n">
-        <v>0.108541412290622</v>
+        <v>0.01973775154567289</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>72.49202521291146</v>
+        <v>72.88155538552094</v>
       </c>
       <c r="D37" t="n">
-        <v>11.53443605310187</v>
+        <v>11.4834089020222</v>
       </c>
       <c r="E37" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F37" t="n">
-        <v>86.15444717406365</v>
+        <v>85.61475776838557</v>
       </c>
       <c r="G37" t="n">
-        <v>6.776450925113714</v>
+        <v>6.573987816482141</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0001120180872908706</v>
+        <v>0.00011015376407515</v>
       </c>
       <c r="K37" t="n">
-        <v>0.003360542618726118</v>
+        <v>0.003304612922254501</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -1928,31 +1940,31 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>74.13640010186913</v>
+        <v>74.36776840376352</v>
       </c>
       <c r="D38" t="n">
-        <v>11.59429546743251</v>
+        <v>11.45154043127563</v>
       </c>
       <c r="E38" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F38" t="n">
-        <v>82.9317475257071</v>
+        <v>83.20067557832489</v>
       </c>
       <c r="G38" t="n">
-        <v>5.823143050067576</v>
+        <v>5.499362140651325</v>
       </c>
       <c r="H38" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="J38" t="n">
-        <v>0.007964601923596564</v>
+        <v>0.0045446626448536</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2389380577078969</v>
+        <v>0.136339879345608</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1968,28 +1980,28 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>65.83060900972922</v>
+        <v>66.53007329518296</v>
       </c>
       <c r="D39" t="n">
-        <v>11.27929810143768</v>
+        <v>10.84993597916094</v>
       </c>
       <c r="E39" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F39" t="n">
-        <v>68.98938782047476</v>
+        <v>70.62388856322153</v>
       </c>
       <c r="G39" t="n">
-        <v>10.14193629065019</v>
+        <v>10.85219288656299</v>
       </c>
       <c r="H39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2827186640222156</v>
+        <v>0.177749859196961</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -2008,31 +2020,31 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>73.50136683236107</v>
+        <v>74.08221996331557</v>
       </c>
       <c r="D40" t="n">
-        <v>10.421035483683</v>
+        <v>10.11299022321712</v>
       </c>
       <c r="E40" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F40" t="n">
-        <v>83.16552971154967</v>
+        <v>81.84380001592413</v>
       </c>
       <c r="G40" t="n">
-        <v>7.22723842339676</v>
+        <v>8.059509466338874</v>
       </c>
       <c r="H40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="J40" t="n">
-        <v>0.001789577528961105</v>
+        <v>0.006347018919467256</v>
       </c>
       <c r="K40" t="n">
-        <v>0.05368732586883317</v>
+        <v>0.1904105675840177</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2048,34 +2060,34 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>69.75185361829905</v>
+        <v>69.81385562329224</v>
       </c>
       <c r="D41" t="n">
-        <v>11.22581207164695</v>
+        <v>11.30136569738928</v>
       </c>
       <c r="E41" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F41" t="n">
-        <v>79.61316264805046</v>
+        <v>80.83890172779881</v>
       </c>
       <c r="G41" t="n">
-        <v>6.307690393573362</v>
+        <v>6.803067151369868</v>
       </c>
       <c r="H41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J41" t="n">
-        <v>0.003456721195665545</v>
+        <v>0.0006913349424598512</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1037016358699664</v>
+        <v>0.02074004827379554</v>
       </c>
       <c r="L41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>69.38207706644923</v>
+        <v>69.31585597603505</v>
       </c>
       <c r="D42" t="n">
-        <v>10.63176948993316</v>
+        <v>10.92080755910686</v>
       </c>
       <c r="E42" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F42" t="n">
-        <v>74.85354272398042</v>
+        <v>75.24352916556637</v>
       </c>
       <c r="G42" t="n">
-        <v>9.923958043219196</v>
+        <v>10.68748771816</v>
       </c>
       <c r="H42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="J42" t="n">
-        <v>0.115899421366369</v>
+        <v>0.09173078082796643</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>62.86643296962779</v>
+        <v>62.75175363436446</v>
       </c>
       <c r="D43" t="n">
-        <v>10.89137083324228</v>
+        <v>10.66606813975092</v>
       </c>
       <c r="E43" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F43" t="n">
-        <v>79.31418155799255</v>
+        <v>79.24258413461257</v>
       </c>
       <c r="G43" t="n">
-        <v>8.836876187007149</v>
+        <v>8.801101251496062</v>
       </c>
       <c r="H43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="J43" t="n">
-        <v>2.617237044951947e-05</v>
+        <v>9.760890921017671e-06</v>
       </c>
       <c r="K43" t="n">
-        <v>0.000785171113485584</v>
+        <v>0.0002928267276305301</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,31 +2180,31 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>73.50139898934748</v>
+        <v>73.86288856695001</v>
       </c>
       <c r="D44" t="n">
-        <v>10.27311527424253</v>
+        <v>10.26741909403584</v>
       </c>
       <c r="E44" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F44" t="n">
-        <v>83.72671492919415</v>
+        <v>82.84421039463538</v>
       </c>
       <c r="G44" t="n">
-        <v>5.518343143833549</v>
+        <v>5.683668378031868</v>
       </c>
       <c r="H44" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0005310672490430397</v>
+        <v>0.001178641779073899</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01593201747129119</v>
+        <v>0.03535925337221697</v>
       </c>
       <c r="L44" t="b">
         <v>1</v>
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>69.19403506886708</v>
+        <v>68.56526121084592</v>
       </c>
       <c r="D45" t="n">
-        <v>10.00762008067658</v>
+        <v>9.580567406355724</v>
       </c>
       <c r="E45" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F45" t="n">
-        <v>80.81769530534011</v>
+        <v>80.70042139337789</v>
       </c>
       <c r="G45" t="n">
-        <v>5.078669081722857</v>
+        <v>5.163557182548964</v>
       </c>
       <c r="H45" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J45" t="n">
-        <v>8.350611867783973e-05</v>
+        <v>1.811391485500635e-05</v>
       </c>
       <c r="K45" t="n">
-        <v>0.002505183560335192</v>
+        <v>0.0005434174456501905</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>75.05996137095023</v>
+        <v>75.42079998992305</v>
       </c>
       <c r="D46" t="n">
-        <v>11.97103679406409</v>
+        <v>12.11267669240365</v>
       </c>
       <c r="E46" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F46" t="n">
-        <v>83.78164529838641</v>
+        <v>83.47363935109763</v>
       </c>
       <c r="G46" t="n">
-        <v>8.229357004575341</v>
+        <v>7.752191100961031</v>
       </c>
       <c r="H46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="J46" t="n">
-        <v>0.009810853119502394</v>
+        <v>0.01293748100436516</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2943255935850718</v>
+        <v>0.3881244301309548</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>66.54284596871919</v>
+        <v>66.86440405426221</v>
       </c>
       <c r="D47" t="n">
-        <v>10.69032045487067</v>
+        <v>10.58966114060267</v>
       </c>
       <c r="E47" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F47" t="n">
-        <v>78.22113114978491</v>
+        <v>77.90269648181217</v>
       </c>
       <c r="G47" t="n">
-        <v>5.124644198491293</v>
+        <v>4.867281046918974</v>
       </c>
       <c r="H47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0001986833491849266</v>
+        <v>0.0001532184483022871</v>
       </c>
       <c r="K47" t="n">
-        <v>0.005960500475547797</v>
+        <v>0.004596553449068614</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,31 +2340,31 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>67.521121508839</v>
+        <v>67.6466543912277</v>
       </c>
       <c r="D48" t="n">
-        <v>10.76842820360538</v>
+        <v>10.9824515182462</v>
       </c>
       <c r="E48" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F48" t="n">
-        <v>74.95754712494775</v>
+        <v>74.64435598379045</v>
       </c>
       <c r="G48" t="n">
-        <v>3.282810687189079</v>
+        <v>3.197269856162134</v>
       </c>
       <c r="H48" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="J48" t="n">
-        <v>0.004738318021681464</v>
+        <v>0.004945494107994238</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1421495406504439</v>
+        <v>0.1483648232398271</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2368,31 +2380,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>75.90618078768348</v>
+        <v>75.48959491457801</v>
       </c>
       <c r="D49" t="n">
-        <v>10.33114190388118</v>
+        <v>10.20295776081762</v>
       </c>
       <c r="E49" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F49" t="n">
-        <v>82.54603478333591</v>
+        <v>81.33980751763116</v>
       </c>
       <c r="G49" t="n">
-        <v>6.126375706421045</v>
+        <v>7.240476355099547</v>
       </c>
       <c r="H49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02793036516394929</v>
+        <v>0.04149949882070393</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8379109549184788</v>
+        <v>1</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.83429739681731</v>
+        <v>75.85928221676863</v>
       </c>
       <c r="D50" t="n">
-        <v>8.237883265732018</v>
+        <v>8.22433366321386</v>
       </c>
       <c r="E50" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F50" t="n">
-        <v>85.36533262253977</v>
+        <v>84.92456345372003</v>
       </c>
       <c r="G50" t="n">
-        <v>4.606930514218465</v>
+        <v>4.991363846703189</v>
       </c>
       <c r="H50" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="J50" t="n">
-        <v>5.490400360792369e-05</v>
+        <v>6.636153936068702e-05</v>
       </c>
       <c r="K50" t="n">
-        <v>0.001647120108237711</v>
+        <v>0.001990846180820611</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>68.47632422425946</v>
+        <v>68.4347347310684</v>
       </c>
       <c r="D51" t="n">
-        <v>8.12140491207316</v>
+        <v>8.174967543051508</v>
       </c>
       <c r="E51" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F51" t="n">
-        <v>79.84646771395535</v>
+        <v>78.92398492416133</v>
       </c>
       <c r="G51" t="n">
-        <v>4.6663273029828</v>
+        <v>5.00147453178001</v>
       </c>
       <c r="H51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="J51" t="n">
-        <v>1.213302230311436e-05</v>
+        <v>2.173100739955307e-05</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0003639906690934309</v>
+        <v>0.0006519302219865921</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,31 +2500,31 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>71.39041594500617</v>
+        <v>71.3020006481008</v>
       </c>
       <c r="D52" t="n">
-        <v>9.684786704717377</v>
+        <v>9.934027778077303</v>
       </c>
       <c r="E52" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F52" t="n">
-        <v>78.45129504700894</v>
+        <v>80.23186182773175</v>
       </c>
       <c r="G52" t="n">
-        <v>5.756708497070031</v>
+        <v>7.161202817029691</v>
       </c>
       <c r="H52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J52" t="n">
-        <v>0.007964601923596564</v>
+        <v>0.001714796117382557</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2389380577078969</v>
+        <v>0.0514438835214767</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>73.38917269597394</v>
+        <v>73.68785971252791</v>
       </c>
       <c r="D53" t="n">
-        <v>9.762928902994942</v>
+        <v>9.727700598639638</v>
       </c>
       <c r="E53" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F53" t="n">
-        <v>84.11549564571021</v>
+        <v>84.15430990450652</v>
       </c>
       <c r="G53" t="n">
-        <v>5.885876829226016</v>
+        <v>5.623255329221617</v>
       </c>
       <c r="H53" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0002101793267766415</v>
+        <v>0.0001230474849486408</v>
       </c>
       <c r="K53" t="n">
-        <v>0.006305379803299245</v>
+        <v>0.003691424548459224</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,28 +2580,28 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>67.50555921005567</v>
+        <v>67.38225684801841</v>
       </c>
       <c r="D54" t="n">
-        <v>9.673116759907494</v>
+        <v>9.53890353976986</v>
       </c>
       <c r="E54" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F54" t="n">
-        <v>68.29491612750404</v>
+        <v>67.65574372935924</v>
       </c>
       <c r="G54" t="n">
-        <v>9.488366152315052</v>
+        <v>9.276435675885793</v>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8254524006382234</v>
+        <v>0.9945964156639604</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>68.07671645874935</v>
+        <v>68.51155113785795</v>
       </c>
       <c r="D55" t="n">
-        <v>11.30412261670633</v>
+        <v>11.35343598907956</v>
       </c>
       <c r="E55" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F55" t="n">
-        <v>75.81857162890171</v>
+        <v>76.54694797971882</v>
       </c>
       <c r="G55" t="n">
-        <v>8.707570881766122</v>
+        <v>8.47528719330206</v>
       </c>
       <c r="H55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01411311427746458</v>
+        <v>0.008426643686018996</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4233934283239373</v>
+        <v>0.2527993105805699</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>61.90367738202725</v>
+        <v>62.31908398312367</v>
       </c>
       <c r="D56" t="n">
-        <v>10.2328917422521</v>
+        <v>10.71357201646038</v>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F56" t="n">
-        <v>76.27635968913593</v>
+        <v>75.86458514153085</v>
       </c>
       <c r="G56" t="n">
-        <v>10.05143642339737</v>
+        <v>9.616975095698111</v>
       </c>
       <c r="H56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="J56" t="n">
-        <v>9.397172726661528e-05</v>
+        <v>7.869736477544053e-05</v>
       </c>
       <c r="K56" t="n">
-        <v>0.002819151817998459</v>
+        <v>0.002360920943263216</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,31 +2700,31 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>71.96022493726142</v>
+        <v>72.15980923974733</v>
       </c>
       <c r="D57" t="n">
-        <v>11.1081536634925</v>
+        <v>11.23525238672679</v>
       </c>
       <c r="E57" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F57" t="n">
-        <v>78.64725734506177</v>
+        <v>78.20252603789568</v>
       </c>
       <c r="G57" t="n">
-        <v>6.685247774797425</v>
+        <v>7.337065278835064</v>
       </c>
       <c r="H57" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02502945776115344</v>
+        <v>0.04016485741588768</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7508837328346033</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>68.06917181277508</v>
+        <v>68.11314688896189</v>
       </c>
       <c r="D58" t="n">
-        <v>9.582689439046737</v>
+        <v>9.620399401338265</v>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F58" t="n">
-        <v>82.26338962932711</v>
+        <v>82.20603502999676</v>
       </c>
       <c r="G58" t="n">
-        <v>4.691776655351063</v>
+        <v>4.466240095228232</v>
       </c>
       <c r="H58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I58" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="J58" t="n">
-        <v>1.136575587102216e-05</v>
+        <v>4.25570184800483e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0003409726761306648</v>
+        <v>0.0001276710554401449</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>72.32866043060294</v>
+        <v>72.62414433821773</v>
       </c>
       <c r="D59" t="n">
-        <v>10.5975139482383</v>
+        <v>10.18806361431963</v>
       </c>
       <c r="E59" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F59" t="n">
-        <v>71.74673171322146</v>
+        <v>71.28243911792734</v>
       </c>
       <c r="G59" t="n">
-        <v>6.101938536192917</v>
+        <v>5.848605232094878</v>
       </c>
       <c r="H59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I59" t="n">
-        <v>397</v>
+        <v>459</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9037385284327787</v>
+        <v>0.886905248410112</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,31 +2820,31 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>68.85506135776075</v>
+        <v>68.81366429568878</v>
       </c>
       <c r="D60" t="n">
-        <v>10.25657534761666</v>
+        <v>10.40168104168773</v>
       </c>
       <c r="E60" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F60" t="n">
-        <v>76.39965181849426</v>
+        <v>77.90052809368615</v>
       </c>
       <c r="G60" t="n">
-        <v>7.203988274287767</v>
+        <v>7.977155712872256</v>
       </c>
       <c r="H60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I60" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J60" t="n">
-        <v>0.01925559407901325</v>
+        <v>0.0045446626448536</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5776678223703976</v>
+        <v>0.136339879345608</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>68.92790800401173</v>
+        <v>68.64190246714499</v>
       </c>
       <c r="D61" t="n">
-        <v>9.810358937400808</v>
+        <v>10.03748579050308</v>
       </c>
       <c r="E61" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F61" t="n">
-        <v>78.51466808040759</v>
+        <v>78.03712219701775</v>
       </c>
       <c r="G61" t="n">
-        <v>8.15783064993334</v>
+        <v>7.800815147094966</v>
       </c>
       <c r="H61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="J61" t="n">
-        <v>0.001269901043570018</v>
+        <v>0.0008833350461222578</v>
       </c>
       <c r="K61" t="n">
-        <v>0.03809703130710053</v>
+        <v>0.02650005138366773</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>99.99810613232832</v>
+        <v>100.1515152035903</v>
       </c>
       <c r="D62" t="n">
-        <v>20.9211443522397</v>
+        <v>21.50336705508746</v>
       </c>
       <c r="E62" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F62" t="n">
-        <v>101.9741575350771</v>
+        <v>101.7184206057172</v>
       </c>
       <c r="G62" t="n">
-        <v>7.752173049837036</v>
+        <v>7.300075119397847</v>
       </c>
       <c r="H62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I62" t="n">
-        <v>464</v>
+        <v>519</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4132865042989008</v>
+        <v>0.3396211397544819</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>105.0484224601538</v>
+        <v>105.1890530103916</v>
       </c>
       <c r="D63" t="n">
-        <v>13.42019777533042</v>
+        <v>13.76454168066818</v>
       </c>
       <c r="E63" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F63" t="n">
-        <v>33.64724596660058</v>
+        <v>35.59018221058587</v>
       </c>
       <c r="G63" t="n">
-        <v>6.734095188365615</v>
+        <v>8.199518886620833</v>
       </c>
       <c r="H63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I63" t="n">
-        <v>812</v>
+        <v>896</v>
       </c>
       <c r="J63" t="n">
-        <v>7.948289470597983e-09</v>
+        <v>1.349970277860479e-09</v>
       </c>
       <c r="K63" t="n">
-        <v>2.384486841179395e-07</v>
+        <v>4.049910833581437e-08</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,31 +2980,31 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>82.45455654567267</v>
+        <v>82.2759160567707</v>
       </c>
       <c r="D64" t="n">
-        <v>22.74289988382971</v>
+        <v>23.05529804860038</v>
       </c>
       <c r="E64" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F64" t="n">
-        <v>102.6913792406289</v>
+        <v>105.7628205491081</v>
       </c>
       <c r="G64" t="n">
-        <v>10.98271050452084</v>
+        <v>13.37004091499654</v>
       </c>
       <c r="H64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J64" t="n">
-        <v>0.001624034999686472</v>
+        <v>0.0003229419390179111</v>
       </c>
       <c r="K64" t="n">
-        <v>0.04872104999059416</v>
+        <v>0.009688258170537332</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>101.411550016104</v>
+        <v>101.9091169989079</v>
       </c>
       <c r="D65" t="n">
-        <v>14.32995341708304</v>
+        <v>14.30431561369023</v>
       </c>
       <c r="E65" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F65" t="n">
-        <v>51.55424406615175</v>
+        <v>49.95398174356067</v>
       </c>
       <c r="G65" t="n">
-        <v>10.55644243781731</v>
+        <v>16.51181171853596</v>
       </c>
       <c r="H65" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I65" t="n">
-        <v>810</v>
+        <v>891</v>
       </c>
       <c r="J65" t="n">
-        <v>9.406641579982645e-09</v>
+        <v>2.052335266900335e-09</v>
       </c>
       <c r="K65" t="n">
-        <v>2.821992473994794e-07</v>
+        <v>6.157005800701006e-08</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>81.00649452941212</v>
+        <v>80.47553566374164</v>
       </c>
       <c r="D66" t="n">
-        <v>24.69968377382691</v>
+        <v>24.60057988781673</v>
       </c>
       <c r="E66" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F66" t="n">
-        <v>76.44518782095341</v>
+        <v>77.98251627512025</v>
       </c>
       <c r="G66" t="n">
-        <v>10.53885259412426</v>
+        <v>10.70885434463812</v>
       </c>
       <c r="H66" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I66" t="n">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4812472901827335</v>
+        <v>0.6597860122395971</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,31 +3100,31 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>102.0471843797883</v>
+        <v>102.1203213578097</v>
       </c>
       <c r="D67" t="n">
-        <v>18.29654807213528</v>
+        <v>18.84880377859839</v>
       </c>
       <c r="E67" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F67" t="n">
-        <v>115.4293097731587</v>
+        <v>114.8616038069624</v>
       </c>
       <c r="G67" t="n">
-        <v>5.697624965396966</v>
+        <v>5.554790719811312</v>
       </c>
       <c r="H67" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I67" t="n">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="J67" t="n">
-        <v>0.01853398904560368</v>
+        <v>0.03637736470152856</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5560196713681105</v>
+        <v>1</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>97.85765472344475</v>
+        <v>97.63069689862904</v>
       </c>
       <c r="D68" t="n">
-        <v>16.11808051660098</v>
+        <v>16.16150124863773</v>
       </c>
       <c r="E68" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F68" t="n">
-        <v>93.01214225061644</v>
+        <v>92.16534036229817</v>
       </c>
       <c r="G68" t="n">
-        <v>13.28664676781644</v>
+        <v>12.75029514749962</v>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I68" t="n">
-        <v>496</v>
+        <v>555</v>
       </c>
       <c r="J68" t="n">
-        <v>0.2028663952103028</v>
+        <v>0.1491529689594686</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>80.66149594464014</v>
+        <v>81.07659182806997</v>
       </c>
       <c r="D69" t="n">
-        <v>14.42071701340133</v>
+        <v>14.34870473469088</v>
       </c>
       <c r="E69" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F69" t="n">
-        <v>42.11777970967607</v>
+        <v>43.85323273422017</v>
       </c>
       <c r="G69" t="n">
-        <v>5.382772908843439</v>
+        <v>7.096689727075176</v>
       </c>
       <c r="H69" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I69" t="n">
-        <v>803</v>
+        <v>880</v>
       </c>
       <c r="J69" t="n">
-        <v>1.68577870496219e-08</v>
+        <v>5.077379017688145e-09</v>
       </c>
       <c r="K69" t="n">
-        <v>5.057336114886571e-07</v>
+        <v>1.523213705306444e-07</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -3208,34 +3220,34 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>100.1164112749736</v>
+        <v>100.9003854474139</v>
       </c>
       <c r="D70" t="n">
-        <v>16.70486421797423</v>
+        <v>16.77531441395887</v>
       </c>
       <c r="E70" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F70" t="n">
-        <v>74.95686789858873</v>
+        <v>72.65548577696001</v>
       </c>
       <c r="G70" t="n">
-        <v>28.66583877273825</v>
+        <v>29.6296301269838</v>
       </c>
       <c r="H70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I70" t="n">
-        <v>594</v>
+        <v>685</v>
       </c>
       <c r="J70" t="n">
-        <v>0.00763508338748834</v>
+        <v>0.001358320303066038</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2290525016246502</v>
+        <v>0.04074960909198114</v>
       </c>
       <c r="L70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3248,28 +3260,28 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>88.57198707750553</v>
+        <v>89.44096427560534</v>
       </c>
       <c r="D71" t="n">
-        <v>19.29619049610553</v>
+        <v>19.22195163362782</v>
       </c>
       <c r="E71" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F71" t="n">
-        <v>87.69037159839867</v>
+        <v>90.66881722332278</v>
       </c>
       <c r="G71" t="n">
-        <v>14.26217601868346</v>
+        <v>15.4964764829198</v>
       </c>
       <c r="H71" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I71" t="n">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9150176217691511</v>
+        <v>0.7095323568099448</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>94.3688458572862</v>
+        <v>93.20151025029291</v>
       </c>
       <c r="D72" t="n">
-        <v>21.01171726898829</v>
+        <v>20.99683281818282</v>
       </c>
       <c r="E72" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F72" t="n">
-        <v>28.60248958796648</v>
+        <v>32.53048577696001</v>
       </c>
       <c r="G72" t="n">
-        <v>12.0066442549175</v>
+        <v>21.6866680602971</v>
       </c>
       <c r="H72" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I72" t="n">
-        <v>805</v>
+        <v>852</v>
       </c>
       <c r="J72" t="n">
-        <v>1.428362067206341e-08</v>
+        <v>4.619698085921189e-08</v>
       </c>
       <c r="K72" t="n">
-        <v>4.285086201619022e-07</v>
+        <v>1.385909425776357e-06</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>69.25871048342218</v>
+        <v>67.66479317455813</v>
       </c>
       <c r="D73" t="n">
-        <v>30.94589890568511</v>
+        <v>30.00031183557266</v>
       </c>
       <c r="E73" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F73" t="n">
-        <v>103.4291569285509</v>
+        <v>102.722401287857</v>
       </c>
       <c r="G73" t="n">
-        <v>19.34111504567739</v>
+        <v>18.87558117401931</v>
       </c>
       <c r="H73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I73" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0005310672490430397</v>
+        <v>0.0001450824855023217</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01593201747129119</v>
+        <v>0.004352474565069649</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,31 +3380,31 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>96.93212479381569</v>
+        <v>98.11617736848466</v>
       </c>
       <c r="D74" t="n">
-        <v>25.30809235753813</v>
+        <v>24.38965684266241</v>
       </c>
       <c r="E74" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F74" t="n">
-        <v>82.4149658323561</v>
+        <v>81.37756333144631</v>
       </c>
       <c r="G74" t="n">
-        <v>14.98843170841357</v>
+        <v>15.76519162429838</v>
       </c>
       <c r="H74" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I74" t="n">
-        <v>550</v>
+        <v>629</v>
       </c>
       <c r="J74" t="n">
-        <v>0.04117609590991505</v>
+        <v>0.01449120007195416</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0.4347360021586247</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>82.06431585933603</v>
+        <v>80.18036634183811</v>
       </c>
       <c r="D75" t="n">
-        <v>15.99232883001738</v>
+        <v>13.68843182523414</v>
       </c>
       <c r="E75" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F75" t="n">
-        <v>37.46445432857543</v>
+        <v>39.37745931219922</v>
       </c>
       <c r="G75" t="n">
-        <v>14.66994851642971</v>
+        <v>14.84006064062837</v>
       </c>
       <c r="H75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I75" t="n">
-        <v>796</v>
+        <v>877</v>
       </c>
       <c r="J75" t="n">
-        <v>2.992081436653717e-08</v>
+        <v>6.475845129038062e-09</v>
       </c>
       <c r="K75" t="n">
-        <v>8.976244309961151e-07</v>
+        <v>1.942753538711419e-07</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,28 +3460,28 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>104.4346685926776</v>
+        <v>104.0168568800288</v>
       </c>
       <c r="D76" t="n">
-        <v>17.28450870761908</v>
+        <v>17.29275059751525</v>
       </c>
       <c r="E76" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F76" t="n">
-        <v>112.6655036189396</v>
+        <v>112.2774642654965</v>
       </c>
       <c r="G76" t="n">
-        <v>20.38900094527706</v>
+        <v>19.10054664620942</v>
       </c>
       <c r="H76" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I76" t="n">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1742109534142038</v>
+        <v>0.1650304072680473</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -3488,31 +3500,31 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>78.69779439179352</v>
+        <v>79.3428889854837</v>
       </c>
       <c r="D77" t="n">
-        <v>15.59194595241268</v>
+        <v>15.14202892817326</v>
       </c>
       <c r="E77" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F77" t="n">
-        <v>90.35279406412987</v>
+        <v>89.52520379281046</v>
       </c>
       <c r="G77" t="n">
-        <v>16.28338350646273</v>
+        <v>16.86831339736756</v>
       </c>
       <c r="H77" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I77" t="n">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02502945776115344</v>
+        <v>0.04016485741588768</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7508837328346033</v>
+        <v>1</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>84.01242169885893</v>
+        <v>84.93349197363622</v>
       </c>
       <c r="D78" t="n">
-        <v>18.54948898478406</v>
+        <v>17.26052490332503</v>
       </c>
       <c r="E78" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F78" t="n">
-        <v>74.69653390481575</v>
+        <v>72.72688862156802</v>
       </c>
       <c r="G78" t="n">
-        <v>9.070216032130523</v>
+        <v>10.06935507218936</v>
       </c>
       <c r="H78" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I78" t="n">
-        <v>578</v>
+        <v>664</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01468144339203379</v>
+        <v>0.003512443053041098</v>
       </c>
       <c r="K78" t="n">
-        <v>0.4404433017610138</v>
+        <v>0.1053732915912329</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3568,31 +3580,31 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>101.3059951979852</v>
+        <v>99.86706138045339</v>
       </c>
       <c r="D79" t="n">
-        <v>14.44088026274194</v>
+        <v>12.5851005882632</v>
       </c>
       <c r="E79" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F79" t="n">
-        <v>68.22057539120938</v>
+        <v>67.51086293518253</v>
       </c>
       <c r="G79" t="n">
-        <v>5.415665065981627</v>
+        <v>5.965612282928529</v>
       </c>
       <c r="H79" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I79" t="n">
-        <v>797</v>
+        <v>880</v>
       </c>
       <c r="J79" t="n">
-        <v>2.758251592018246e-08</v>
+        <v>5.077379017688145e-09</v>
       </c>
       <c r="K79" t="n">
-        <v>8.274754776054739e-07</v>
+        <v>1.523213705306444e-07</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>95.51710366299986</v>
+        <v>95.58789939751706</v>
       </c>
       <c r="D80" t="n">
-        <v>14.54782350364337</v>
+        <v>14.71370890171891</v>
       </c>
       <c r="E80" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F80" t="n">
-        <v>106.0326019974928</v>
+        <v>104.1122265072174</v>
       </c>
       <c r="G80" t="n">
-        <v>10.08347083655077</v>
+        <v>10.71397074483289</v>
       </c>
       <c r="H80" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I80" t="n">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="J80" t="n">
-        <v>0.009030904423048408</v>
+        <v>0.02247090188705861</v>
       </c>
       <c r="K80" t="n">
-        <v>0.2709271326914522</v>
+        <v>0.6741270566117583</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>87.54518578525607</v>
+        <v>87.30532155998525</v>
       </c>
       <c r="D81" t="n">
-        <v>22.57309597170754</v>
+        <v>22.02403737178173</v>
       </c>
       <c r="E81" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F81" t="n">
-        <v>63.9753572439448</v>
+        <v>63.40789838664021</v>
       </c>
       <c r="G81" t="n">
-        <v>8.474078769377305</v>
+        <v>9.093751648987078</v>
       </c>
       <c r="H81" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I81" t="n">
-        <v>657</v>
+        <v>733</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0003650036548845403</v>
+        <v>0.0001164324168782946</v>
       </c>
       <c r="K81" t="n">
-        <v>0.01095010964653621</v>
+        <v>0.003492972506348839</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,31 +3700,31 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>93.56962540382769</v>
+        <v>93.32151783187065</v>
       </c>
       <c r="D82" t="n">
-        <v>20.15982281810375</v>
+        <v>20.05042640605189</v>
       </c>
       <c r="E82" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F82" t="n">
-        <v>71.22833528769551</v>
+        <v>74.45852356354365</v>
       </c>
       <c r="G82" t="n">
-        <v>14.6506746533748</v>
+        <v>16.52359428470369</v>
       </c>
       <c r="H82" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I82" t="n">
-        <v>655</v>
+        <v>681</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0004066691557942478</v>
+        <v>0.001637266288409364</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01220007467382743</v>
+        <v>0.04911798865228092</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -3728,31 +3740,31 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>90.55230408854429</v>
+        <v>91.47290323884987</v>
       </c>
       <c r="D83" t="n">
-        <v>17.29530324631096</v>
+        <v>16.46513904659949</v>
       </c>
       <c r="E83" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F83" t="n">
-        <v>73.97825724798831</v>
+        <v>75.81549674497587</v>
       </c>
       <c r="G83" t="n">
-        <v>11.37934915745297</v>
+        <v>14.74323957435173</v>
       </c>
       <c r="H83" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I83" t="n">
-        <v>642</v>
+        <v>681</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0008059288274436602</v>
+        <v>0.001637266288409364</v>
       </c>
       <c r="K83" t="n">
-        <v>0.02417786482330981</v>
+        <v>0.04911798865228092</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -3768,28 +3780,28 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>78.75853704480895</v>
+        <v>78.7248386640248</v>
       </c>
       <c r="D84" t="n">
-        <v>17.80300181881211</v>
+        <v>17.40876153130857</v>
       </c>
       <c r="E84" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F84" t="n">
-        <v>61.8763636731227</v>
+        <v>58.42423648457392</v>
       </c>
       <c r="G84" t="n">
-        <v>38.17631421516946</v>
+        <v>38.19588763680739</v>
       </c>
       <c r="H84" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I84" t="n">
-        <v>497</v>
+        <v>582</v>
       </c>
       <c r="J84" t="n">
-        <v>0.1978658378562647</v>
+        <v>0.07056890828494211</v>
       </c>
       <c r="K84" t="n">
         <v>1</v>
@@ -3808,31 +3820,31 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>85.76402568882536</v>
+        <v>85.10705460757734</v>
       </c>
       <c r="D85" t="n">
-        <v>21.51370861962894</v>
+        <v>21.68482000111015</v>
       </c>
       <c r="E85" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F85" t="n">
-        <v>66.02776070518777</v>
+        <v>68.68260508066793</v>
       </c>
       <c r="G85" t="n">
-        <v>13.03873392430578</v>
+        <v>14.89295760528435</v>
       </c>
       <c r="H85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I85" t="n">
-        <v>624</v>
+        <v>650</v>
       </c>
       <c r="J85" t="n">
-        <v>0.001970504691539685</v>
+        <v>0.006347018919467256</v>
       </c>
       <c r="K85" t="n">
-        <v>0.05911514074619056</v>
+        <v>0.1904105675840177</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>67.1370586685145</v>
+        <v>66.63960626339401</v>
       </c>
       <c r="D86" t="n">
-        <v>20.07217706481372</v>
+        <v>20.4347232468824</v>
       </c>
       <c r="E86" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F86" t="n">
-        <v>71.39383486312705</v>
+        <v>70.14397572884218</v>
       </c>
       <c r="G86" t="n">
-        <v>42.47309036995517</v>
+        <v>41.15938010587778</v>
       </c>
       <c r="H86" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I86" t="n">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8365491752833986</v>
+        <v>0.9406150519002542</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,31 +3900,31 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>104.1169760972893</v>
+        <v>104.4079122356554</v>
       </c>
       <c r="D87" t="n">
-        <v>13.7977636799713</v>
+        <v>13.66858681764282</v>
       </c>
       <c r="E87" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F87" t="n">
-        <v>83.25435364522257</v>
+        <v>82.98020733088023</v>
       </c>
       <c r="G87" t="n">
-        <v>5.204726547182312</v>
+        <v>5.797971382347329</v>
       </c>
       <c r="H87" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I87" t="n">
-        <v>720</v>
+        <v>804</v>
       </c>
       <c r="J87" t="n">
-        <v>8.174836200890552e-06</v>
+        <v>1.47048753847021e-06</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0002452450860267166</v>
+        <v>4.411462615410629e-05</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,31 +3940,31 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>79.91808153664448</v>
+        <v>79.7695800816787</v>
       </c>
       <c r="D88" t="n">
-        <v>22.55861158194246</v>
+        <v>22.7916144874546</v>
       </c>
       <c r="E88" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F88" t="n">
-        <v>114.3411103473369</v>
+        <v>114.6371582224734</v>
       </c>
       <c r="G88" t="n">
-        <v>8.652674676442821</v>
+        <v>8.138697066752945</v>
       </c>
       <c r="H88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I88" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J88" t="n">
-        <v>1.267931181082021e-06</v>
+        <v>3.402863743691864e-07</v>
       </c>
       <c r="K88" t="n">
-        <v>3.803793543246064e-05</v>
+        <v>1.020859123107559e-05</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>94.21366241447612</v>
+        <v>94.6899208483278</v>
       </c>
       <c r="D89" t="n">
-        <v>23.23492343734637</v>
+        <v>21.63402712178154</v>
       </c>
       <c r="E89" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>20.00330556791067</v>
+        <v>21.68357734220204</v>
       </c>
       <c r="G89" t="n">
-        <v>5.395809626314221</v>
+        <v>8.585169969523305</v>
       </c>
       <c r="H89" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I89" t="n">
-        <v>812</v>
+        <v>896</v>
       </c>
       <c r="J89" t="n">
-        <v>7.948289470597983e-09</v>
+        <v>1.349970277860479e-09</v>
       </c>
       <c r="K89" t="n">
-        <v>2.384486841179395e-07</v>
+        <v>4.049910833581437e-08</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,31 +4020,31 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>80.83349317274553</v>
+        <v>80.07630787271026</v>
       </c>
       <c r="D90" t="n">
-        <v>17.63070524664741</v>
+        <v>17.04266185402215</v>
       </c>
       <c r="E90" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F90" t="n">
-        <v>104.5286235898261</v>
+        <v>106.5749840786862</v>
       </c>
       <c r="G90" t="n">
-        <v>11.25731150966967</v>
+        <v>11.8471513455853</v>
       </c>
       <c r="H90" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I90" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="J90" t="n">
-        <v>3.575857418612665e-05</v>
+        <v>2.515787075891889e-06</v>
       </c>
       <c r="K90" t="n">
-        <v>0.001072757225583799</v>
+        <v>7.547361227675668e-05</v>
       </c>
       <c r="L90" t="b">
         <v>1</v>
@@ -4048,28 +4060,28 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>81.26701035556367</v>
+        <v>79.87756045044671</v>
       </c>
       <c r="D91" t="n">
-        <v>17.29440628458883</v>
+        <v>16.60301830435293</v>
       </c>
       <c r="E91" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F91" t="n">
-        <v>91.21867736848461</v>
+        <v>88.56923259269718</v>
       </c>
       <c r="G91" t="n">
-        <v>24.88550168668699</v>
+        <v>24.81703451523944</v>
       </c>
       <c r="H91" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I91" t="n">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="J91" t="n">
-        <v>0.06334170542912894</v>
+        <v>0.08663393465986578</v>
       </c>
       <c r="K91" t="n">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>10.76284883916645</v>
+        <v>10.79261143523465</v>
       </c>
       <c r="D92" t="n">
-        <v>4.839471110549679</v>
+        <v>4.672693401860873</v>
       </c>
       <c r="E92" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F92" t="n">
-        <v>10.71736553391284</v>
+        <v>10.59464082329968</v>
       </c>
       <c r="G92" t="n">
-        <v>1.400976433271519</v>
+        <v>1.350959881420714</v>
       </c>
       <c r="H92" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I92" t="n">
-        <v>460</v>
+        <v>519</v>
       </c>
       <c r="J92" t="n">
-        <v>0.4465311486764828</v>
+        <v>0.3396211397544819</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,31 +4140,31 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>11.30861077759198</v>
+        <v>11.28419432693348</v>
       </c>
       <c r="D93" t="n">
-        <v>5.351731259093029</v>
+        <v>5.418210070125181</v>
       </c>
       <c r="E93" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F93" t="n">
-        <v>13.8098221065191</v>
+        <v>13.68524887460674</v>
       </c>
       <c r="G93" t="n">
-        <v>0.7304003294311174</v>
+        <v>1.332559204575911</v>
       </c>
       <c r="H93" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I93" t="n">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="J93" t="n">
-        <v>0.02077278035020222</v>
+        <v>0.02587165426938799</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6231834105060665</v>
+        <v>0.7761496280816397</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4168,28 +4180,28 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>13.47610594312342</v>
+        <v>13.25478534238293</v>
       </c>
       <c r="D94" t="n">
-        <v>4.295413441628965</v>
+        <v>4.117879667679087</v>
       </c>
       <c r="E94" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F94" t="n">
-        <v>13.31255520431402</v>
+        <v>12.73013036934587</v>
       </c>
       <c r="G94" t="n">
-        <v>1.953184905537941</v>
+        <v>2.4997535853389</v>
       </c>
       <c r="H94" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I94" t="n">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="J94" t="n">
-        <v>0.9150176217691511</v>
+        <v>0.7605490867327631</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>12.83931704014568</v>
+        <v>12.6162618350301</v>
       </c>
       <c r="D95" t="n">
-        <v>3.914834393684175</v>
+        <v>3.54076271993152</v>
       </c>
       <c r="E95" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F95" t="n">
-        <v>16.22353640772933</v>
+        <v>16.13606207289289</v>
       </c>
       <c r="G95" t="n">
-        <v>1.938343710969871</v>
+        <v>2.13240245561372</v>
       </c>
       <c r="H95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I95" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0004527446282884041</v>
+        <v>0.0002233916830319775</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01358233884865212</v>
+        <v>0.006701750490959324</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,28 +4260,28 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>14.93306598815785</v>
+        <v>15.11920219112698</v>
       </c>
       <c r="D96" t="n">
-        <v>5.117884454467436</v>
+        <v>5.069741857494143</v>
       </c>
       <c r="E96" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F96" t="n">
-        <v>13.97004129670087</v>
+        <v>13.97398375637267</v>
       </c>
       <c r="G96" t="n">
-        <v>1.953421697920657</v>
+        <v>1.827302522000743</v>
       </c>
       <c r="H96" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I96" t="n">
-        <v>498</v>
+        <v>567</v>
       </c>
       <c r="J96" t="n">
-        <v>0.1929560604215034</v>
+        <v>0.1084787575995715</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
@@ -4288,28 +4300,28 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>12.20795751652319</v>
+        <v>12.15533021864779</v>
       </c>
       <c r="D97" t="n">
-        <v>5.122962412357382</v>
+        <v>5.15011464959421</v>
       </c>
       <c r="E97" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F97" t="n">
-        <v>12.64358390280938</v>
+        <v>12.84957628267704</v>
       </c>
       <c r="G97" t="n">
-        <v>1.354149851994696</v>
+        <v>1.570119094979666</v>
       </c>
       <c r="H97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I97" t="n">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="J97" t="n">
-        <v>0.6540163995069548</v>
+        <v>0.5740393354177287</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
@@ -4328,28 +4340,28 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>13.08441066238761</v>
+        <v>13.05462602466952</v>
       </c>
       <c r="D98" t="n">
-        <v>4.441931793477009</v>
+        <v>4.456231736293319</v>
       </c>
       <c r="E98" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F98" t="n">
-        <v>11.48255504935456</v>
+        <v>11.75962821347214</v>
       </c>
       <c r="G98" t="n">
-        <v>1.981302702934643</v>
+        <v>1.996275407053988</v>
       </c>
       <c r="H98" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I98" t="n">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="J98" t="n">
-        <v>0.3022841965606107</v>
+        <v>0.4202887426699178</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -4368,28 +4380,28 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>12.85529004941066</v>
+        <v>12.77049629646843</v>
       </c>
       <c r="D99" t="n">
-        <v>5.114364455596597</v>
+        <v>5.03675999160594</v>
       </c>
       <c r="E99" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F99" t="n">
-        <v>15.03277392961735</v>
+        <v>14.97164212495927</v>
       </c>
       <c r="G99" t="n">
-        <v>2.528260928528771</v>
+        <v>2.493489876169503</v>
       </c>
       <c r="H99" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I99" t="n">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="J99" t="n">
-        <v>0.3368508232173144</v>
+        <v>0.3001165975807645</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
@@ -4408,28 +4420,28 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>12.40544780083108</v>
+        <v>12.26094362574183</v>
       </c>
       <c r="D100" t="n">
-        <v>3.166492239825236</v>
+        <v>3.001670187960844</v>
       </c>
       <c r="E100" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F100" t="n">
-        <v>12.24222180899691</v>
+        <v>12.43273233268246</v>
       </c>
       <c r="G100" t="n">
-        <v>1.74601243359789</v>
+        <v>1.738186174479265</v>
       </c>
       <c r="H100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I100" t="n">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="J100" t="n">
-        <v>0.6643165323892645</v>
+        <v>0.9406150519002542</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4448,28 +4460,28 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>12.94236593467011</v>
+        <v>12.79657859157326</v>
       </c>
       <c r="D101" t="n">
-        <v>3.91973608115971</v>
+        <v>3.547744947920183</v>
       </c>
       <c r="E101" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F101" t="n">
-        <v>13.63052314319802</v>
+        <v>13.42158788914195</v>
       </c>
       <c r="G101" t="n">
-        <v>1.973877977403848</v>
+        <v>1.930468577141368</v>
       </c>
       <c r="H101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I101" t="n">
-        <v>311</v>
+        <v>353</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1787645672028489</v>
+        <v>0.2005482175951804</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>12.56100641104761</v>
+        <v>12.62889141989366</v>
       </c>
       <c r="D102" t="n">
-        <v>4.039643695992274</v>
+        <v>4.088987231372487</v>
       </c>
       <c r="E102" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F102" t="n">
-        <v>17.23197395131168</v>
+        <v>17.20104437845749</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7037213096771961</v>
+        <v>1.262359580557334</v>
       </c>
       <c r="H102" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I102" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="J102" t="n">
-        <v>1.686172810103181e-06</v>
+        <v>1.926116027853009e-06</v>
       </c>
       <c r="K102" t="n">
-        <v>5.058518430309543e-05</v>
+        <v>5.778348083559027e-05</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,28 +4540,28 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>14.80498473916308</v>
+        <v>14.9589068771016</v>
       </c>
       <c r="D103" t="n">
-        <v>3.764036867196495</v>
+        <v>3.88033021441039</v>
       </c>
       <c r="E103" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F103" t="n">
-        <v>13.06203996404935</v>
+        <v>13.32594166937841</v>
       </c>
       <c r="G103" t="n">
-        <v>1.653515794562215</v>
+        <v>1.764022751635379</v>
       </c>
       <c r="H103" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I103" t="n">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="J103" t="n">
-        <v>0.1003081183556453</v>
+        <v>0.1275589063493808</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4568,28 +4580,28 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>12.86711981627145</v>
+        <v>12.68838694931272</v>
       </c>
       <c r="D104" t="n">
-        <v>4.700280634876084</v>
+        <v>4.516275739759805</v>
       </c>
       <c r="E104" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F104" t="n">
-        <v>11.07784234422694</v>
+        <v>10.85290161622732</v>
       </c>
       <c r="G104" t="n">
-        <v>0.5314784161287517</v>
+        <v>0.8492454205968333</v>
       </c>
       <c r="H104" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I104" t="n">
-        <v>488</v>
+        <v>549</v>
       </c>
       <c r="J104" t="n">
-        <v>0.2462110697505323</v>
+        <v>0.1734313738703956</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -4608,28 +4620,28 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>14.85355964630761</v>
+        <v>15.08533424759421</v>
       </c>
       <c r="D105" t="n">
-        <v>2.874135288253436</v>
+        <v>2.811659642825797</v>
       </c>
       <c r="E105" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F105" t="n">
-        <v>15.50580207025859</v>
+        <v>15.27745993328991</v>
       </c>
       <c r="G105" t="n">
-        <v>2.290332939425797</v>
+        <v>2.468090839536718</v>
       </c>
       <c r="H105" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I105" t="n">
-        <v>330</v>
+        <v>406</v>
       </c>
       <c r="J105" t="n">
-        <v>0.2827186640222156</v>
+        <v>0.5740393354177287</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
@@ -4648,28 +4660,28 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>11.49606257317157</v>
+        <v>11.45248593742733</v>
       </c>
       <c r="D106" t="n">
-        <v>3.096328524870565</v>
+        <v>2.964085396576295</v>
       </c>
       <c r="E106" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F106" t="n">
-        <v>12.27576162583481</v>
+        <v>12.27390036880352</v>
       </c>
       <c r="G106" t="n">
-        <v>2.656466757424269</v>
+        <v>2.488532325163487</v>
       </c>
       <c r="H106" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I106" t="n">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="J106" t="n">
-        <v>0.3158169995847975</v>
+        <v>0.2580561232057301</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -4688,28 +4700,28 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>14.60062361838927</v>
+        <v>14.49576979994727</v>
       </c>
       <c r="D107" t="n">
-        <v>3.76507457060492</v>
+        <v>3.673515672626632</v>
       </c>
       <c r="E107" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F107" t="n">
-        <v>16.01317426742902</v>
+        <v>16.17763416585308</v>
       </c>
       <c r="G107" t="n">
-        <v>1.402391025875684</v>
+        <v>1.383059529343506</v>
       </c>
       <c r="H107" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I107" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="J107" t="n">
-        <v>0.1032847681205466</v>
+        <v>0.04874902704445291</v>
       </c>
       <c r="K107" t="n">
         <v>1</v>
@@ -4728,28 +4740,28 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>13.22119236509304</v>
+        <v>13.25885118853916</v>
       </c>
       <c r="D108" t="n">
-        <v>5.416084189328707</v>
+        <v>5.383508373134506</v>
       </c>
       <c r="E108" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F108" t="n">
-        <v>13.42413106472651</v>
+        <v>13.61962421358059</v>
       </c>
       <c r="G108" t="n">
-        <v>1.251961884491311</v>
+        <v>1.400316352565917</v>
       </c>
       <c r="H108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I108" t="n">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="J108" t="n">
-        <v>0.5359635055507652</v>
+        <v>0.4522068978286441</v>
       </c>
       <c r="K108" t="n">
         <v>1</v>
@@ -4768,28 +4780,28 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>11.68023964750455</v>
+        <v>11.83185182387302</v>
       </c>
       <c r="D109" t="n">
-        <v>5.528765164641575</v>
+        <v>5.39437796595826</v>
       </c>
       <c r="E109" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F109" t="n">
-        <v>11.67521113228887</v>
+        <v>11.46536941371078</v>
       </c>
       <c r="G109" t="n">
-        <v>1.593816300736286</v>
+        <v>1.726524591033021</v>
       </c>
       <c r="H109" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I109" t="n">
-        <v>478</v>
+        <v>540</v>
       </c>
       <c r="J109" t="n">
-        <v>0.3090016290700639</v>
+        <v>0.2152134681600496</v>
       </c>
       <c r="K109" t="n">
         <v>1</v>
@@ -4808,28 +4820,28 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>13.59800309331175</v>
+        <v>13.74484236747087</v>
       </c>
       <c r="D110" t="n">
-        <v>3.529722078330347</v>
+        <v>3.61501003133702</v>
       </c>
       <c r="E110" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F110" t="n">
-        <v>14.98162451768857</v>
+        <v>15.18360349549837</v>
       </c>
       <c r="G110" t="n">
-        <v>2.304136364528852</v>
+        <v>2.306389374933035</v>
       </c>
       <c r="H110" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I110" t="n">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="J110" t="n">
-        <v>0.06966224169604796</v>
+        <v>0.06447568641110425</v>
       </c>
       <c r="K110" t="n">
         <v>1</v>
@@ -4848,28 +4860,28 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>12.75579032807055</v>
+        <v>12.81754247826689</v>
       </c>
       <c r="D111" t="n">
-        <v>4.122568801830939</v>
+        <v>3.994854430224262</v>
       </c>
       <c r="E111" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F111" t="n">
-        <v>13.04058388731343</v>
+        <v>13.3986857983512</v>
       </c>
       <c r="G111" t="n">
-        <v>1.405011219672596</v>
+        <v>1.907030934827484</v>
       </c>
       <c r="H111" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I111" t="n">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="J111" t="n">
-        <v>0.499141350249255</v>
+        <v>0.8442964921241434</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>12.95702250973436</v>
+        <v>12.80621358452261</v>
       </c>
       <c r="D112" t="n">
-        <v>4.11937940578552</v>
+        <v>3.801305851705572</v>
       </c>
       <c r="E112" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F112" t="n">
-        <v>15.99308338369512</v>
+        <v>15.92834499403402</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8808412847739319</v>
+        <v>1.284019080585757</v>
       </c>
       <c r="H112" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I112" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="J112" t="n">
-        <v>0.009030904423048408</v>
+        <v>0.00336280985598261</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2709271326914522</v>
+        <v>0.1008842956794783</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4928,28 +4940,28 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>12.74713831255537</v>
+        <v>12.40471222087921</v>
       </c>
       <c r="D113" t="n">
-        <v>4.95423571113917</v>
+        <v>4.623404048286494</v>
       </c>
       <c r="E113" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F113" t="n">
-        <v>14.02642795159061</v>
+        <v>13.89333475702349</v>
       </c>
       <c r="G113" t="n">
-        <v>1.070907809648847</v>
+        <v>1.068476470641192</v>
       </c>
       <c r="H113" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I113" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="J113" t="n">
-        <v>0.1003081183556453</v>
+        <v>0.05882340701657349</v>
       </c>
       <c r="K113" t="n">
         <v>1</v>
@@ -4968,31 +4980,31 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>16.3537363802641</v>
+        <v>16.37572821269733</v>
       </c>
       <c r="D114" t="n">
-        <v>4.205734584981808</v>
+        <v>3.623934222196465</v>
       </c>
       <c r="E114" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F114" t="n">
-        <v>13.63878015898838</v>
+        <v>13.79954408016049</v>
       </c>
       <c r="G114" t="n">
-        <v>3.990817671663685</v>
+        <v>4.115190645999384</v>
       </c>
       <c r="H114" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I114" t="n">
-        <v>568</v>
+        <v>617</v>
       </c>
       <c r="J114" t="n">
-        <v>0.02156971642411823</v>
+        <v>0.02247090188705861</v>
       </c>
       <c r="K114" t="n">
-        <v>0.6470914927235469</v>
+        <v>0.6741270566117583</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -5008,31 +5020,31 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.71941950843643</v>
+        <v>12.76572838702675</v>
       </c>
       <c r="D115" t="n">
-        <v>3.310731773032709</v>
+        <v>3.353862598607429</v>
       </c>
       <c r="E115" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F115" t="n">
-        <v>14.48476205972133</v>
+        <v>14.15810317008347</v>
       </c>
       <c r="G115" t="n">
-        <v>1.343946222282769</v>
+        <v>1.75863901531509</v>
       </c>
       <c r="H115" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I115" t="n">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="J115" t="n">
-        <v>0.02156971642411823</v>
+        <v>0.0376045574486133</v>
       </c>
       <c r="K115" t="n">
-        <v>0.6470914927235469</v>
+        <v>1</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -5048,28 +5060,28 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>13.28510806019049</v>
+        <v>13.3756255520431</v>
       </c>
       <c r="D116" t="n">
-        <v>3.309099365484296</v>
+        <v>3.168323498768262</v>
       </c>
       <c r="E116" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F116" t="n">
-        <v>14.8872243658283</v>
+        <v>15.22557930632385</v>
       </c>
       <c r="G116" t="n">
-        <v>2.795246671272675</v>
+        <v>2.824721715929843</v>
       </c>
       <c r="H116" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I116" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J116" t="n">
-        <v>0.1192350814557705</v>
+        <v>0.04573076438204</v>
       </c>
       <c r="K116" t="n">
         <v>1</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>10.63820707609095</v>
+        <v>10.52197674058231</v>
       </c>
       <c r="D117" t="n">
-        <v>3.886147216692021</v>
+        <v>3.896133736772055</v>
       </c>
       <c r="E117" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F117" t="n">
-        <v>14.89470968341775</v>
+        <v>15.03592004284626</v>
       </c>
       <c r="G117" t="n">
-        <v>1.826024422209964</v>
+        <v>1.752411099855134</v>
       </c>
       <c r="H117" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I117" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J117" t="n">
-        <v>0.0001120180872908706</v>
+        <v>1.704134321865496e-05</v>
       </c>
       <c r="K117" t="n">
-        <v>0.003360542618726118</v>
+        <v>0.0005112402965596488</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,28 +5140,28 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>13.61190867384044</v>
+        <v>13.78527920497562</v>
       </c>
       <c r="D118" t="n">
-        <v>5.434821571133434</v>
+        <v>5.385752922393044</v>
       </c>
       <c r="E118" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F118" t="n">
-        <v>11.87241868191295</v>
+        <v>11.86333660086528</v>
       </c>
       <c r="G118" t="n">
-        <v>1.449844974093044</v>
+        <v>1.370688642485975</v>
       </c>
       <c r="H118" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I118" t="n">
-        <v>489</v>
+        <v>541</v>
       </c>
       <c r="J118" t="n">
-        <v>0.2404632093542003</v>
+        <v>0.2102415646665226</v>
       </c>
       <c r="K118" t="n">
         <v>1</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>12.53038156692337</v>
+        <v>12.40938161554505</v>
       </c>
       <c r="D119" t="n">
-        <v>4.395728893754452</v>
+        <v>4.243607217622008</v>
       </c>
       <c r="E119" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F119" t="n">
-        <v>17.99446650699216</v>
+        <v>18.22465217685231</v>
       </c>
       <c r="G119" t="n">
-        <v>1.563071154510895</v>
+        <v>1.685467887894254</v>
       </c>
       <c r="H119" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I119" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="J119" t="n">
-        <v>1.906351221823521e-05</v>
+        <v>1.04521229526199e-06</v>
       </c>
       <c r="K119" t="n">
-        <v>0.0005719053665470564</v>
+        <v>3.135636885785969e-05</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,28 +5220,28 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>15.36777587139363</v>
+        <v>15.38235165726644</v>
       </c>
       <c r="D120" t="n">
-        <v>4.387298355235479</v>
+        <v>4.451419483864791</v>
       </c>
       <c r="E120" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F120" t="n">
-        <v>14.85636444410102</v>
+        <v>14.70298066522441</v>
       </c>
       <c r="G120" t="n">
-        <v>2.577044113514175</v>
+        <v>2.636436894057419</v>
       </c>
       <c r="H120" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I120" t="n">
-        <v>489</v>
+        <v>548</v>
       </c>
       <c r="J120" t="n">
-        <v>0.2404632093542003</v>
+        <v>0.177749859196961</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
@@ -5248,28 +5260,28 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>14.44580406930116</v>
+        <v>14.43257745499494</v>
       </c>
       <c r="D121" t="n">
-        <v>3.328753854121291</v>
+        <v>3.197062934224547</v>
       </c>
       <c r="E121" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F121" t="n">
-        <v>13.82893069612913</v>
+        <v>13.64029137371548</v>
       </c>
       <c r="G121" t="n">
-        <v>3.488885096953358</v>
+        <v>3.380563291368611</v>
       </c>
       <c r="H121" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I121" t="n">
-        <v>489</v>
+        <v>553</v>
       </c>
       <c r="J121" t="n">
-        <v>0.2404632093542003</v>
+        <v>0.1569395152032713</v>
       </c>
       <c r="K121" t="n">
         <v>1</v>
